--- a/artfynd/A 4009-2026 artfynd.xlsx
+++ b/artfynd/A 4009-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78599217</v>
+        <v>79934419</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600473.7111476808</v>
+        <v>600486</v>
       </c>
       <c r="R2" t="n">
-        <v>6757711.29934881</v>
+        <v>6757789</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,16 +769,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Våtmark,ej i anknytning till sötvattenstränder</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Öppen källa med ca 40 m2 vitmossa och vide runt om.</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -807,6 +781,688 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>110297997</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kattmuren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>600317</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6757690</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Urban Selander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Urban Selander, Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96799405</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kappmuren skogen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>600395</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6757759</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-10-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-10-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86046071</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58209</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kappmuren 1,Ockelbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>600358</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6757757</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-05-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Två familjer byggt bo på varsin byggnad. Bona byggda av lera under takfoten. Möjligt att förra årets ungar har följt med tillbaka.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Hustak</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Roof tops</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>109144104</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kappmuren 1,Ockelbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600358</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6757757</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89084905</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kappmuren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>600363</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6757770</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-11-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78599217</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kappmuren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>600474</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6757711</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-06-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Våtmark,ej i anknytning till sötvattenstränder</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Öppen källa med ca 40 m2 vitmossa och vide runt om.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
